--- a/Team-Data/2008-09/3-5-2008-09.xlsx
+++ b/Team-Data/2008-09/3-5-2008-09.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -775,7 +842,7 @@
         <v>16</v>
       </c>
       <c r="AP2" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AQ2" t="n">
         <v>29</v>
@@ -793,13 +860,13 @@
         <v>16</v>
       </c>
       <c r="AV2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AW2" t="n">
         <v>11</v>
       </c>
       <c r="AX2" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AY2" t="n">
         <v>10</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>3-5-2008-09</t>
+          <t>2009-03-05</t>
         </is>
       </c>
     </row>
@@ -843,58 +910,58 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E3" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F3" t="n">
         <v>14</v>
       </c>
       <c r="G3" t="n">
-        <v>0.77</v>
+        <v>0.774</v>
       </c>
       <c r="H3" t="n">
         <v>48.4</v>
       </c>
       <c r="I3" t="n">
-        <v>37.5</v>
+        <v>37.4</v>
       </c>
       <c r="J3" t="n">
         <v>76.90000000000001</v>
       </c>
       <c r="K3" t="n">
-        <v>0.488</v>
+        <v>0.487</v>
       </c>
       <c r="L3" t="n">
-        <v>6.6</v>
+        <v>6.5</v>
       </c>
       <c r="M3" t="n">
-        <v>16.7</v>
+        <v>16.6</v>
       </c>
       <c r="N3" t="n">
-        <v>0.395</v>
+        <v>0.392</v>
       </c>
       <c r="O3" t="n">
         <v>20.3</v>
       </c>
       <c r="P3" t="n">
-        <v>26.2</v>
+        <v>26.3</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.775</v>
+        <v>0.772</v>
       </c>
       <c r="R3" t="n">
         <v>10.7</v>
       </c>
       <c r="S3" t="n">
-        <v>31.9</v>
+        <v>31.8</v>
       </c>
       <c r="T3" t="n">
-        <v>42.6</v>
+        <v>42.5</v>
       </c>
       <c r="U3" t="n">
-        <v>22.9</v>
+        <v>22.8</v>
       </c>
       <c r="V3" t="n">
         <v>15.9</v>
@@ -903,28 +970,28 @@
         <v>8</v>
       </c>
       <c r="X3" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="Y3" t="n">
         <v>4.5</v>
       </c>
       <c r="Z3" t="n">
-        <v>23.3</v>
+        <v>23.4</v>
       </c>
       <c r="AA3" t="n">
-        <v>22.7</v>
+        <v>22.8</v>
       </c>
       <c r="AB3" t="n">
-        <v>101.9</v>
+        <v>101.7</v>
       </c>
       <c r="AC3" t="n">
         <v>9.1</v>
       </c>
       <c r="AD3" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="AE3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AF3" t="n">
         <v>3</v>
@@ -933,7 +1000,7 @@
         <v>3</v>
       </c>
       <c r="AH3" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AI3" t="n">
         <v>9</v>
@@ -945,31 +1012,31 @@
         <v>2</v>
       </c>
       <c r="AL3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AM3" t="n">
         <v>21</v>
       </c>
       <c r="AN3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AO3" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AP3" t="n">
         <v>7</v>
       </c>
       <c r="AQ3" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AR3" t="n">
         <v>20</v>
       </c>
       <c r="AS3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AT3" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AU3" t="n">
         <v>3</v>
@@ -981,7 +1048,7 @@
         <v>7</v>
       </c>
       <c r="AX3" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="AY3" t="n">
         <v>12</v>
@@ -990,7 +1057,7 @@
         <v>27</v>
       </c>
       <c r="BA3" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BB3" t="n">
         <v>9</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>3-5-2008-09</t>
+          <t>2009-03-05</t>
         </is>
       </c>
     </row>
@@ -1109,7 +1176,7 @@
         <v>21</v>
       </c>
       <c r="AF4" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AG4" t="n">
         <v>20</v>
@@ -1124,7 +1191,7 @@
         <v>30</v>
       </c>
       <c r="AK4" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AL4" t="n">
         <v>23</v>
@@ -1154,7 +1221,7 @@
         <v>26</v>
       </c>
       <c r="AU4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AV4" t="n">
         <v>25</v>
@@ -1178,7 +1245,7 @@
         <v>30</v>
       </c>
       <c r="BC4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BD4" t="n">
         <v>10</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>3-5-2008-09</t>
+          <t>2009-03-05</t>
         </is>
       </c>
     </row>
@@ -1207,16 +1274,16 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E5" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F5" t="n">
         <v>34</v>
       </c>
       <c r="G5" t="n">
-        <v>0.443</v>
+        <v>0.452</v>
       </c>
       <c r="H5" t="n">
         <v>48.6</v>
@@ -1225,43 +1292,43 @@
         <v>37.6</v>
       </c>
       <c r="J5" t="n">
-        <v>83.59999999999999</v>
+        <v>83.3</v>
       </c>
       <c r="K5" t="n">
-        <v>0.45</v>
+        <v>0.451</v>
       </c>
       <c r="L5" t="n">
         <v>5.8</v>
       </c>
       <c r="M5" t="n">
-        <v>15.6</v>
+        <v>15.5</v>
       </c>
       <c r="N5" t="n">
         <v>0.375</v>
       </c>
       <c r="O5" t="n">
-        <v>19.4</v>
+        <v>19.6</v>
       </c>
       <c r="P5" t="n">
-        <v>24.5</v>
+        <v>24.8</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.79</v>
+        <v>0.789</v>
       </c>
       <c r="R5" t="n">
         <v>12.2</v>
       </c>
       <c r="S5" t="n">
-        <v>30.4</v>
+        <v>30.3</v>
       </c>
       <c r="T5" t="n">
-        <v>42.6</v>
+        <v>42.5</v>
       </c>
       <c r="U5" t="n">
         <v>21</v>
       </c>
       <c r="V5" t="n">
-        <v>14.8</v>
+        <v>14.9</v>
       </c>
       <c r="W5" t="n">
         <v>7.5</v>
@@ -1273,19 +1340,19 @@
         <v>5.5</v>
       </c>
       <c r="Z5" t="n">
-        <v>21.6</v>
+        <v>21.5</v>
       </c>
       <c r="AA5" t="n">
-        <v>20.7</v>
+        <v>20.8</v>
       </c>
       <c r="AB5" t="n">
-        <v>100.5</v>
+        <v>100.6</v>
       </c>
       <c r="AC5" t="n">
-        <v>-1.6</v>
+        <v>-1.4</v>
       </c>
       <c r="AD5" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="AE5" t="n">
         <v>18</v>
@@ -1297,7 +1364,7 @@
         <v>18</v>
       </c>
       <c r="AH5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AI5" t="n">
         <v>8</v>
@@ -1306,7 +1373,7 @@
         <v>6</v>
       </c>
       <c r="AK5" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AL5" t="n">
         <v>24</v>
@@ -1318,10 +1385,10 @@
         <v>11</v>
       </c>
       <c r="AO5" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AP5" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="AQ5" t="n">
         <v>8</v>
@@ -1330,16 +1397,16 @@
         <v>6</v>
       </c>
       <c r="AS5" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AT5" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AU5" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AV5" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AW5" t="n">
         <v>10</v>
@@ -1348,7 +1415,7 @@
         <v>4</v>
       </c>
       <c r="AY5" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AZ5" t="n">
         <v>19</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>3-5-2008-09</t>
+          <t>2009-03-05</t>
         </is>
       </c>
     </row>
@@ -1389,43 +1456,43 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E6" t="n">
         <v>48</v>
       </c>
       <c r="F6" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G6" t="n">
-        <v>0.8139999999999999</v>
+        <v>0.8</v>
       </c>
       <c r="H6" t="n">
         <v>48.1</v>
       </c>
       <c r="I6" t="n">
-        <v>36.8</v>
+        <v>36.7</v>
       </c>
       <c r="J6" t="n">
-        <v>78.3</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="K6" t="n">
-        <v>0.47</v>
+        <v>0.469</v>
       </c>
       <c r="L6" t="n">
-        <v>8.1</v>
+        <v>8</v>
       </c>
       <c r="M6" t="n">
-        <v>20.6</v>
+        <v>20.5</v>
       </c>
       <c r="N6" t="n">
-        <v>0.391</v>
+        <v>0.389</v>
       </c>
       <c r="O6" t="n">
-        <v>18.6</v>
+        <v>18.7</v>
       </c>
       <c r="P6" t="n">
-        <v>24.6</v>
+        <v>24.7</v>
       </c>
       <c r="Q6" t="n">
         <v>0.755</v>
@@ -1434,7 +1501,7 @@
         <v>10.8</v>
       </c>
       <c r="S6" t="n">
-        <v>30.9</v>
+        <v>31</v>
       </c>
       <c r="T6" t="n">
         <v>41.7</v>
@@ -1443,49 +1510,49 @@
         <v>20</v>
       </c>
       <c r="V6" t="n">
-        <v>13</v>
+        <v>13.2</v>
       </c>
       <c r="W6" t="n">
         <v>7.8</v>
       </c>
       <c r="X6" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="Y6" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="Z6" t="n">
-        <v>20.3</v>
+        <v>20.4</v>
       </c>
       <c r="AA6" t="n">
-        <v>20.4</v>
+        <v>20.5</v>
       </c>
       <c r="AB6" t="n">
-        <v>100.2</v>
+        <v>100</v>
       </c>
       <c r="AC6" t="n">
-        <v>9.9</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="AD6" t="n">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="AE6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AF6" t="n">
         <v>1</v>
       </c>
       <c r="AG6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AH6" t="n">
+        <v>28</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>16</v>
+      </c>
+      <c r="AJ6" t="n">
         <v>26</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>15</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>25</v>
       </c>
       <c r="AK6" t="n">
         <v>5</v>
@@ -1500,16 +1567,16 @@
         <v>4</v>
       </c>
       <c r="AO6" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AP6" t="n">
         <v>15</v>
       </c>
       <c r="AQ6" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AR6" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AS6" t="n">
         <v>10</v>
@@ -1521,7 +1588,7 @@
         <v>25</v>
       </c>
       <c r="AV6" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AW6" t="n">
         <v>8</v>
@@ -1530,10 +1597,10 @@
         <v>5</v>
       </c>
       <c r="AY6" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AZ6" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="BA6" t="n">
         <v>21</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>3-5-2008-09</t>
+          <t>2009-03-05</t>
         </is>
       </c>
     </row>
@@ -1571,88 +1638,88 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E7" t="n">
         <v>37</v>
       </c>
       <c r="F7" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G7" t="n">
-        <v>0.597</v>
+        <v>0.607</v>
       </c>
       <c r="H7" t="n">
         <v>48.4</v>
       </c>
       <c r="I7" t="n">
-        <v>38</v>
+        <v>38.1</v>
       </c>
       <c r="J7" t="n">
-        <v>82.7</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="K7" t="n">
-        <v>0.459</v>
+        <v>0.46</v>
       </c>
       <c r="L7" t="n">
-        <v>6.7</v>
+        <v>6.8</v>
       </c>
       <c r="M7" t="n">
         <v>19.5</v>
       </c>
       <c r="N7" t="n">
-        <v>0.345</v>
+        <v>0.347</v>
       </c>
       <c r="O7" t="n">
-        <v>18.2</v>
+        <v>18.1</v>
       </c>
       <c r="P7" t="n">
         <v>22.1</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.82</v>
+        <v>0.819</v>
       </c>
       <c r="R7" t="n">
         <v>11.2</v>
       </c>
       <c r="S7" t="n">
-        <v>31.7</v>
+        <v>31.9</v>
       </c>
       <c r="T7" t="n">
-        <v>42.9</v>
+        <v>43</v>
       </c>
       <c r="U7" t="n">
-        <v>21.5</v>
+        <v>21.7</v>
       </c>
       <c r="V7" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="W7" t="n">
-        <v>7.2</v>
+        <v>7.3</v>
       </c>
       <c r="X7" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="Y7" t="n">
         <v>4.1</v>
       </c>
       <c r="Z7" t="n">
-        <v>19.2</v>
+        <v>19.1</v>
       </c>
       <c r="AA7" t="n">
         <v>20</v>
       </c>
       <c r="AB7" t="n">
-        <v>100.8</v>
+        <v>101</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="AD7" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="AE7" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AF7" t="n">
         <v>11</v>
@@ -1661,7 +1728,7 @@
         <v>11</v>
       </c>
       <c r="AH7" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AI7" t="n">
         <v>7</v>
@@ -1679,10 +1746,10 @@
         <v>11</v>
       </c>
       <c r="AN7" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AO7" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AP7" t="n">
         <v>29</v>
@@ -1694,31 +1761,31 @@
         <v>13</v>
       </c>
       <c r="AS7" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AT7" t="n">
         <v>4</v>
       </c>
       <c r="AU7" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AV7" t="n">
         <v>10</v>
       </c>
       <c r="AW7" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AX7" t="n">
+        <v>6</v>
+      </c>
+      <c r="AY7" t="n">
         <v>7</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>6</v>
       </c>
       <c r="AZ7" t="n">
         <v>3</v>
       </c>
       <c r="BA7" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BB7" t="n">
         <v>10</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>3-5-2008-09</t>
+          <t>2009-03-05</t>
         </is>
       </c>
     </row>
@@ -1753,28 +1820,28 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E8" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F8" t="n">
         <v>22</v>
       </c>
       <c r="G8" t="n">
-        <v>0.645</v>
+        <v>0.639</v>
       </c>
       <c r="H8" t="n">
         <v>48.2</v>
       </c>
       <c r="I8" t="n">
-        <v>36.8</v>
+        <v>36.7</v>
       </c>
       <c r="J8" t="n">
-        <v>78.59999999999999</v>
+        <v>78.5</v>
       </c>
       <c r="K8" t="n">
-        <v>0.468</v>
+        <v>0.467</v>
       </c>
       <c r="L8" t="n">
         <v>6.4</v>
@@ -1783,31 +1850,31 @@
         <v>17.6</v>
       </c>
       <c r="N8" t="n">
-        <v>0.364</v>
+        <v>0.362</v>
       </c>
       <c r="O8" t="n">
-        <v>22.8</v>
+        <v>23</v>
       </c>
       <c r="P8" t="n">
-        <v>30.2</v>
+        <v>30.4</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.756</v>
+        <v>0.755</v>
       </c>
       <c r="R8" t="n">
-        <v>10.7</v>
+        <v>10.8</v>
       </c>
       <c r="S8" t="n">
         <v>30.4</v>
       </c>
       <c r="T8" t="n">
-        <v>41.1</v>
+        <v>41.2</v>
       </c>
       <c r="U8" t="n">
-        <v>22.1</v>
+        <v>22</v>
       </c>
       <c r="V8" t="n">
-        <v>15.7</v>
+        <v>15.8</v>
       </c>
       <c r="W8" t="n">
         <v>8.699999999999999</v>
@@ -1816,10 +1883,10 @@
         <v>5.9</v>
       </c>
       <c r="Y8" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="Z8" t="n">
-        <v>22.7</v>
+        <v>22.8</v>
       </c>
       <c r="AA8" t="n">
         <v>23.7</v>
@@ -1828,13 +1895,13 @@
         <v>102.8</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
       <c r="AD8" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="AE8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AF8" t="n">
         <v>6</v>
@@ -1843,10 +1910,10 @@
         <v>6</v>
       </c>
       <c r="AH8" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AI8" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AJ8" t="n">
         <v>24</v>
@@ -1861,7 +1928,7 @@
         <v>18</v>
       </c>
       <c r="AN8" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="AO8" t="n">
         <v>1</v>
@@ -1873,10 +1940,10 @@
         <v>21</v>
       </c>
       <c r="AR8" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AS8" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AT8" t="n">
         <v>16</v>
@@ -1894,7 +1961,7 @@
         <v>3</v>
       </c>
       <c r="AY8" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AZ8" t="n">
         <v>25</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>3-5-2008-09</t>
+          <t>2009-03-05</t>
         </is>
       </c>
     </row>
@@ -2082,7 +2149,7 @@
         <v>18</v>
       </c>
       <c r="BA9" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BB9" t="n">
         <v>29</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>3-5-2008-09</t>
+          <t>2009-03-05</t>
         </is>
       </c>
     </row>
@@ -2207,7 +2274,7 @@
         <v>24</v>
       </c>
       <c r="AH10" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AI10" t="n">
         <v>3</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>3-5-2008-09</t>
+          <t>2009-03-05</t>
         </is>
       </c>
     </row>
@@ -2380,13 +2447,13 @@
         <v>3</v>
       </c>
       <c r="AE11" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AF11" t="n">
         <v>9</v>
       </c>
       <c r="AG11" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AH11" t="n">
         <v>21</v>
@@ -2407,10 +2474,10 @@
         <v>5</v>
       </c>
       <c r="AN11" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AO11" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AP11" t="n">
         <v>20</v>
@@ -2431,7 +2498,7 @@
         <v>18</v>
       </c>
       <c r="AV11" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AW11" t="n">
         <v>26</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>3-5-2008-09</t>
+          <t>2009-03-05</t>
         </is>
       </c>
     </row>
@@ -2562,7 +2629,7 @@
         <v>1</v>
       </c>
       <c r="AE12" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AF12" t="n">
         <v>22</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>3-5-2008-09</t>
+          <t>2009-03-05</t>
         </is>
       </c>
     </row>
@@ -2753,7 +2820,7 @@
         <v>28</v>
       </c>
       <c r="AH13" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AI13" t="n">
         <v>25</v>
@@ -2771,7 +2838,7 @@
         <v>14</v>
       </c>
       <c r="AN13" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AO13" t="n">
         <v>29</v>
@@ -2792,10 +2859,10 @@
         <v>22</v>
       </c>
       <c r="AU13" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AV13" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AW13" t="n">
         <v>21</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>3-5-2008-09</t>
+          <t>2009-03-05</t>
         </is>
       </c>
     </row>
@@ -2845,16 +2912,16 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E14" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F14" t="n">
         <v>12</v>
       </c>
       <c r="G14" t="n">
-        <v>0.8</v>
+        <v>0.803</v>
       </c>
       <c r="H14" t="n">
         <v>48.3</v>
@@ -2863,7 +2930,7 @@
         <v>40.7</v>
       </c>
       <c r="J14" t="n">
-        <v>85.59999999999999</v>
+        <v>85.5</v>
       </c>
       <c r="K14" t="n">
         <v>0.476</v>
@@ -2872,34 +2939,34 @@
         <v>6.9</v>
       </c>
       <c r="M14" t="n">
-        <v>19</v>
+        <v>18.9</v>
       </c>
       <c r="N14" t="n">
-        <v>0.361</v>
+        <v>0.364</v>
       </c>
       <c r="O14" t="n">
-        <v>20.6</v>
+        <v>20.5</v>
       </c>
       <c r="P14" t="n">
-        <v>26.7</v>
+        <v>26.6</v>
       </c>
       <c r="Q14" t="n">
         <v>0.77</v>
       </c>
       <c r="R14" t="n">
-        <v>12.8</v>
+        <v>12.7</v>
       </c>
       <c r="S14" t="n">
-        <v>31.7</v>
+        <v>31.8</v>
       </c>
       <c r="T14" t="n">
         <v>44.5</v>
       </c>
       <c r="U14" t="n">
-        <v>23.8</v>
+        <v>23.7</v>
       </c>
       <c r="V14" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="W14" t="n">
         <v>8.6</v>
@@ -2908,34 +2975,34 @@
         <v>5.2</v>
       </c>
       <c r="Y14" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="Z14" t="n">
-        <v>20.7</v>
+        <v>20.6</v>
       </c>
       <c r="AA14" t="n">
-        <v>22.8</v>
+        <v>22.7</v>
       </c>
       <c r="AB14" t="n">
-        <v>108.9</v>
+        <v>108.7</v>
       </c>
       <c r="AC14" t="n">
-        <v>7.9</v>
+        <v>8.1</v>
       </c>
       <c r="AD14" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="AE14" t="n">
         <v>1</v>
       </c>
       <c r="AF14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AG14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AH14" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AI14" t="n">
         <v>1</v>
@@ -2950,13 +3017,13 @@
         <v>12</v>
       </c>
       <c r="AM14" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AN14" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="AO14" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AP14" t="n">
         <v>6</v>
@@ -2965,7 +3032,7 @@
         <v>16</v>
       </c>
       <c r="AR14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AS14" t="n">
         <v>7</v>
@@ -2992,7 +3059,7 @@
         <v>14</v>
       </c>
       <c r="BA14" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BB14" t="n">
         <v>1</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>3-5-2008-09</t>
+          <t>2009-03-05</t>
         </is>
       </c>
     </row>
@@ -3105,7 +3172,7 @@
         <v>-6</v>
       </c>
       <c r="AD15" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AE15" t="n">
         <v>26</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>3-5-2008-09</t>
+          <t>2009-03-05</t>
         </is>
       </c>
     </row>
@@ -3287,7 +3354,7 @@
         <v>-0.2</v>
       </c>
       <c r="AD16" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AE16" t="n">
         <v>14</v>
@@ -3302,7 +3369,7 @@
         <v>19</v>
       </c>
       <c r="AI16" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AJ16" t="n">
         <v>12</v>
@@ -3326,7 +3393,7 @@
         <v>28</v>
       </c>
       <c r="AQ16" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AR16" t="n">
         <v>25</v>
@@ -3347,7 +3414,7 @@
         <v>5</v>
       </c>
       <c r="AX16" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AY16" t="n">
         <v>5</v>
@@ -3362,7 +3429,7 @@
         <v>21</v>
       </c>
       <c r="BC16" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BD16" t="n">
         <v>10</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>3-5-2008-09</t>
+          <t>2009-03-05</t>
         </is>
       </c>
     </row>
@@ -3391,16 +3458,16 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E17" t="n">
         <v>29</v>
       </c>
       <c r="F17" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G17" t="n">
-        <v>0.46</v>
+        <v>0.453</v>
       </c>
       <c r="H17" t="n">
         <v>48.3</v>
@@ -3409,46 +3476,46 @@
         <v>36.5</v>
       </c>
       <c r="J17" t="n">
-        <v>81.59999999999999</v>
+        <v>81.5</v>
       </c>
       <c r="K17" t="n">
-        <v>0.447</v>
+        <v>0.448</v>
       </c>
       <c r="L17" t="n">
         <v>6</v>
       </c>
       <c r="M17" t="n">
-        <v>16.7</v>
+        <v>16.6</v>
       </c>
       <c r="N17" t="n">
-        <v>0.363</v>
+        <v>0.364</v>
       </c>
       <c r="O17" t="n">
-        <v>20.3</v>
+        <v>20.2</v>
       </c>
       <c r="P17" t="n">
-        <v>26</v>
+        <v>25.9</v>
       </c>
       <c r="Q17" t="n">
         <v>0.782</v>
       </c>
       <c r="R17" t="n">
-        <v>12</v>
+        <v>12.1</v>
       </c>
       <c r="S17" t="n">
-        <v>29.1</v>
+        <v>28.9</v>
       </c>
       <c r="T17" t="n">
-        <v>41.1</v>
+        <v>41</v>
       </c>
       <c r="U17" t="n">
         <v>21.6</v>
       </c>
       <c r="V17" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="W17" t="n">
-        <v>7.3</v>
+        <v>7.2</v>
       </c>
       <c r="X17" t="n">
         <v>3.8</v>
@@ -3457,7 +3524,7 @@
         <v>4.7</v>
       </c>
       <c r="Z17" t="n">
-        <v>23.9</v>
+        <v>24</v>
       </c>
       <c r="AA17" t="n">
         <v>23</v>
@@ -3466,16 +3533,16 @@
         <v>99.3</v>
       </c>
       <c r="AC17" t="n">
-        <v>-0.1</v>
+        <v>-0.3</v>
       </c>
       <c r="AD17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE17" t="n">
         <v>16</v>
       </c>
       <c r="AF17" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AG17" t="n">
         <v>17</v>
@@ -3502,10 +3569,10 @@
         <v>18</v>
       </c>
       <c r="AO17" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AP17" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AQ17" t="n">
         <v>11</v>
@@ -3517,16 +3584,16 @@
         <v>24</v>
       </c>
       <c r="AT17" t="n">
+        <v>17</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>10</v>
+      </c>
+      <c r="AV17" t="n">
         <v>15</v>
       </c>
-      <c r="AU17" t="n">
-        <v>9</v>
-      </c>
-      <c r="AV17" t="n">
-        <v>13</v>
-      </c>
       <c r="AW17" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AX17" t="n">
         <v>29</v>
@@ -3541,10 +3608,10 @@
         <v>4</v>
       </c>
       <c r="BB17" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BC17" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BD17" t="n">
         <v>10</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>3-5-2008-09</t>
+          <t>2009-03-05</t>
         </is>
       </c>
     </row>
@@ -3651,7 +3718,7 @@
         <v>-4.7</v>
       </c>
       <c r="AD18" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AE18" t="n">
         <v>25</v>
@@ -3687,7 +3754,7 @@
         <v>18</v>
       </c>
       <c r="AP18" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AQ18" t="n">
         <v>17</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>3-5-2008-09</t>
+          <t>2009-03-05</t>
         </is>
       </c>
     </row>
@@ -3836,13 +3903,13 @@
         <v>9</v>
       </c>
       <c r="AE19" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AF19" t="n">
         <v>17</v>
       </c>
       <c r="AG19" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AH19" t="n">
         <v>7</v>
@@ -3869,7 +3936,7 @@
         <v>14</v>
       </c>
       <c r="AP19" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AQ19" t="n">
         <v>9</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>3-5-2008-09</t>
+          <t>2009-03-05</t>
         </is>
       </c>
     </row>
@@ -3937,46 +4004,46 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E20" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F20" t="n">
         <v>22</v>
       </c>
       <c r="G20" t="n">
-        <v>0.633</v>
+        <v>0.627</v>
       </c>
       <c r="H20" t="n">
         <v>48.1</v>
       </c>
       <c r="I20" t="n">
-        <v>35.1</v>
+        <v>35</v>
       </c>
       <c r="J20" t="n">
-        <v>76.90000000000001</v>
+        <v>77</v>
       </c>
       <c r="K20" t="n">
-        <v>0.457</v>
+        <v>0.455</v>
       </c>
       <c r="L20" t="n">
         <v>7.5</v>
       </c>
       <c r="M20" t="n">
-        <v>19.7</v>
+        <v>19.8</v>
       </c>
       <c r="N20" t="n">
-        <v>0.38</v>
+        <v>0.379</v>
       </c>
       <c r="O20" t="n">
-        <v>18.6</v>
+        <v>18.7</v>
       </c>
       <c r="P20" t="n">
         <v>23.1</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.806</v>
+        <v>0.8070000000000001</v>
       </c>
       <c r="R20" t="n">
         <v>9.699999999999999</v>
@@ -3988,7 +4055,7 @@
         <v>39.6</v>
       </c>
       <c r="U20" t="n">
-        <v>19.9</v>
+        <v>19.8</v>
       </c>
       <c r="V20" t="n">
         <v>12.6</v>
@@ -4000,7 +4067,7 @@
         <v>4.3</v>
       </c>
       <c r="Y20" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="Z20" t="n">
         <v>20.6</v>
@@ -4009,25 +4076,25 @@
         <v>21</v>
       </c>
       <c r="AB20" t="n">
-        <v>96.3</v>
+        <v>96.2</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="AD20" t="n">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="AE20" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AF20" t="n">
         <v>6</v>
       </c>
       <c r="AG20" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AH20" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AI20" t="n">
         <v>28</v>
@@ -4036,7 +4103,7 @@
         <v>28</v>
       </c>
       <c r="AK20" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AL20" t="n">
         <v>8</v>
@@ -4045,7 +4112,7 @@
         <v>9</v>
       </c>
       <c r="AN20" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AO20" t="n">
         <v>21</v>
@@ -4069,7 +4136,7 @@
         <v>26</v>
       </c>
       <c r="AV20" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AW20" t="n">
         <v>13</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>3-5-2008-09</t>
+          <t>2009-03-05</t>
         </is>
       </c>
     </row>
@@ -4197,13 +4264,13 @@
         <v>-2</v>
       </c>
       <c r="AD21" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AE21" t="n">
         <v>22</v>
       </c>
       <c r="AF21" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AG21" t="n">
         <v>22</v>
@@ -4230,7 +4297,7 @@
         <v>16</v>
       </c>
       <c r="AO21" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AP21" t="n">
         <v>23</v>
@@ -4245,10 +4312,10 @@
         <v>8</v>
       </c>
       <c r="AT21" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AU21" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AV21" t="n">
         <v>16</v>
@@ -4263,7 +4330,7 @@
         <v>23</v>
       </c>
       <c r="AZ21" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BA21" t="n">
         <v>29</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>3-5-2008-09</t>
+          <t>2009-03-05</t>
         </is>
       </c>
     </row>
@@ -4415,7 +4482,7 @@
         <v>9</v>
       </c>
       <c r="AP22" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AQ22" t="n">
         <v>12</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>3-5-2008-09</t>
+          <t>2009-03-05</t>
         </is>
       </c>
     </row>
@@ -4561,7 +4628,7 @@
         <v>7</v>
       </c>
       <c r="AD23" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AE23" t="n">
         <v>4</v>
@@ -4579,7 +4646,7 @@
         <v>21</v>
       </c>
       <c r="AJ23" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AK23" t="n">
         <v>9</v>
@@ -4615,7 +4682,7 @@
         <v>29</v>
       </c>
       <c r="AV23" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AW23" t="n">
         <v>17</v>
@@ -4627,7 +4694,7 @@
         <v>2</v>
       </c>
       <c r="AZ23" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BA23" t="n">
         <v>8</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>3-5-2008-09</t>
+          <t>2009-03-05</t>
         </is>
       </c>
     </row>
@@ -4776,7 +4843,7 @@
         <v>30</v>
       </c>
       <c r="AO24" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AP24" t="n">
         <v>8</v>
@@ -4785,7 +4852,7 @@
         <v>26</v>
       </c>
       <c r="AR24" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AS24" t="n">
         <v>18</v>
@@ -4794,7 +4861,7 @@
         <v>10</v>
       </c>
       <c r="AU24" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AV24" t="n">
         <v>18</v>
@@ -4809,7 +4876,7 @@
         <v>15</v>
       </c>
       <c r="AZ24" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BA24" t="n">
         <v>10</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>3-5-2008-09</t>
+          <t>2009-03-05</t>
         </is>
       </c>
     </row>
@@ -4949,7 +5016,7 @@
         <v>1</v>
       </c>
       <c r="AL25" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AM25" t="n">
         <v>19</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>3-5-2008-09</t>
+          <t>2009-03-05</t>
         </is>
       </c>
     </row>
@@ -5044,43 +5111,43 @@
         <v>48.3</v>
       </c>
       <c r="I26" t="n">
-        <v>36.8</v>
+        <v>36.7</v>
       </c>
       <c r="J26" t="n">
-        <v>79.2</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="K26" t="n">
-        <v>0.465</v>
+        <v>0.462</v>
       </c>
       <c r="L26" t="n">
-        <v>7.2</v>
+        <v>7.3</v>
       </c>
       <c r="M26" t="n">
-        <v>19</v>
+        <v>19.1</v>
       </c>
       <c r="N26" t="n">
-        <v>0.379</v>
+        <v>0.381</v>
       </c>
       <c r="O26" t="n">
-        <v>18.7</v>
+        <v>18.5</v>
       </c>
       <c r="P26" t="n">
-        <v>24.5</v>
+        <v>24.3</v>
       </c>
       <c r="Q26" t="n">
         <v>0.762</v>
       </c>
       <c r="R26" t="n">
-        <v>12.9</v>
+        <v>13</v>
       </c>
       <c r="S26" t="n">
         <v>28.2</v>
       </c>
       <c r="T26" t="n">
-        <v>41.1</v>
+        <v>41.3</v>
       </c>
       <c r="U26" t="n">
-        <v>20.4</v>
+        <v>20.5</v>
       </c>
       <c r="V26" t="n">
         <v>12.9</v>
@@ -5095,19 +5162,19 @@
         <v>3.8</v>
       </c>
       <c r="Z26" t="n">
-        <v>20.9</v>
+        <v>20.8</v>
       </c>
       <c r="AA26" t="n">
         <v>21.1</v>
       </c>
       <c r="AB26" t="n">
-        <v>99.40000000000001</v>
+        <v>99.2</v>
       </c>
       <c r="AC26" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="AD26" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AE26" t="n">
         <v>8</v>
@@ -5122,25 +5189,25 @@
         <v>15</v>
       </c>
       <c r="AI26" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AJ26" t="n">
         <v>21</v>
       </c>
       <c r="AK26" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AL26" t="n">
         <v>10</v>
       </c>
       <c r="AM26" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AN26" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AO26" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AP26" t="n">
         <v>18</v>
@@ -5155,10 +5222,10 @@
         <v>29</v>
       </c>
       <c r="AT26" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AU26" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AV26" t="n">
         <v>5</v>
@@ -5167,10 +5234,10 @@
         <v>25</v>
       </c>
       <c r="AX26" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AY26" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AZ26" t="n">
         <v>17</v>
@@ -5179,7 +5246,7 @@
         <v>14</v>
       </c>
       <c r="BB26" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="BC26" t="n">
         <v>5</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>3-5-2008-09</t>
+          <t>2009-03-05</t>
         </is>
       </c>
     </row>
@@ -5301,7 +5368,7 @@
         <v>30</v>
       </c>
       <c r="AH27" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AI27" t="n">
         <v>23</v>
@@ -5322,7 +5389,7 @@
         <v>21</v>
       </c>
       <c r="AO27" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AP27" t="n">
         <v>12</v>
@@ -5361,7 +5428,7 @@
         <v>11</v>
       </c>
       <c r="BB27" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BC27" t="n">
         <v>30</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>3-5-2008-09</t>
+          <t>2009-03-05</t>
         </is>
       </c>
     </row>
@@ -5471,7 +5538,7 @@
         <v>3.7</v>
       </c>
       <c r="AD28" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AE28" t="n">
         <v>5</v>
@@ -5492,7 +5559,7 @@
         <v>17</v>
       </c>
       <c r="AK28" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AL28" t="n">
         <v>5</v>
@@ -5501,7 +5568,7 @@
         <v>8</v>
       </c>
       <c r="AN28" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AO28" t="n">
         <v>30</v>
@@ -5510,7 +5577,7 @@
         <v>30</v>
       </c>
       <c r="AQ28" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AR28" t="n">
         <v>30</v>
@@ -5531,7 +5598,7 @@
         <v>30</v>
       </c>
       <c r="AX28" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AY28" t="n">
         <v>11</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>3-5-2008-09</t>
+          <t>2009-03-05</t>
         </is>
       </c>
     </row>
@@ -5674,7 +5741,7 @@
         <v>19</v>
       </c>
       <c r="AK29" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AL29" t="n">
         <v>22</v>
@@ -5707,7 +5774,7 @@
         <v>8</v>
       </c>
       <c r="AV29" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AW29" t="n">
         <v>29</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>3-5-2008-09</t>
+          <t>2009-03-05</t>
         </is>
       </c>
     </row>
@@ -5847,7 +5914,7 @@
         <v>10</v>
       </c>
       <c r="AH30" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AI30" t="n">
         <v>6</v>
@@ -5865,7 +5932,7 @@
         <v>26</v>
       </c>
       <c r="AN30" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AO30" t="n">
         <v>3</v>
@@ -5874,7 +5941,7 @@
         <v>3</v>
       </c>
       <c r="AQ30" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AR30" t="n">
         <v>9</v>
@@ -5895,7 +5962,7 @@
         <v>1</v>
       </c>
       <c r="AX30" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AY30" t="n">
         <v>16</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>3-5-2008-09</t>
+          <t>2009-03-05</t>
         </is>
       </c>
     </row>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>3-5-2008-09</t>
+          <t>2009-03-05</t>
         </is>
       </c>
     </row>
